--- a/data/trans_dic/IP2906_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida</t>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,14; 55,57</t>
+          <t>25,31; 55,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,86; 54,13</t>
+          <t>30,58; 53,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,52; 50,77</t>
+          <t>32,23; 50,75</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,52; 49,69</t>
+          <t>40,88; 49,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,22; 50,48</t>
+          <t>40,91; 50,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,06; 48,71</t>
+          <t>42,49; 48,81</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,17; 45,44</t>
+          <t>31,58; 45,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,53; 40,34</t>
+          <t>27,78; 40,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,75; 41,21</t>
+          <t>31,6; 40,6</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,15; 47,04</t>
+          <t>39,85; 46,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,55; 46,41</t>
+          <t>39,13; 46,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,5; 45,63</t>
+          <t>40,01; 45,51</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>21257</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24285</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45541</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>13379; 29572</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17842; 31466</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35844; 56438</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>190614</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>230710</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>421324</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>171956; 208051</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>205397; 252992</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>392060; 450408</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>55033</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60547</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>115580</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>45102; 64300</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>49632; 72049</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101588; 130494</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>266905</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>315541</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>582446</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>245618; 288835</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>289224; 343369</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>542294; 616890</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2906_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,31; 55,94</t>
+          <t>24,45; 55,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,58; 53,93</t>
+          <t>30,88; 54,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,23; 50,75</t>
+          <t>31,47; 50,69</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,88; 49,46</t>
+          <t>40,77; 49,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40,91; 50,39</t>
+          <t>41,08; 50,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,49; 48,81</t>
+          <t>42,31; 48,9</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,58; 45,03</t>
+          <t>32,12; 44,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,78; 40,33</t>
+          <t>27,81; 40,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,6; 40,6</t>
+          <t>31,2; 41,05</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,85; 46,86</t>
+          <t>39,82; 46,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,13; 46,46</t>
+          <t>39,33; 46,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,01; 45,51</t>
+          <t>40,31; 45,72</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13379; 29572</t>
+          <t>12927; 29180</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17842; 31466</t>
+          <t>18015; 31744</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35844; 56438</t>
+          <t>35002; 56371</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>171956; 208051</t>
+          <t>171505; 206428</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>205397; 252992</t>
+          <t>206255; 254849</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>392060; 450408</t>
+          <t>390425; 451243</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45102; 64300</t>
+          <t>45875; 63932</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49632; 72049</t>
+          <t>49677; 72384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101588; 130494</t>
+          <t>100273; 131959</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>245618; 288835</t>
+          <t>245440; 286338</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>289224; 343369</t>
+          <t>290695; 342775</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>542294; 616890</t>
+          <t>546326; 619637</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2906_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,45; 55,19</t>
+          <t>32,49; 56,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,88; 54,41</t>
+          <t>30,15; 56,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,47; 50,69</t>
+          <t>34,41; 51,89</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,77; 49,07</t>
+          <t>42,45; 51,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,08; 50,76</t>
+          <t>41,68; 49,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,31; 48,9</t>
+          <t>43,13; 49,73</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,12; 44,77</t>
+          <t>27,92; 40,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,81; 40,52</t>
+          <t>32,34; 45,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,2; 41,05</t>
+          <t>32,26; 41,71</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,82; 46,46</t>
+          <t>39,61; 47,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,33; 46,38</t>
+          <t>40,6; 47,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,31; 45,72</t>
+          <t>41,4; 46,41</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>23602</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24285</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45541</t>
+          <t>42618</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12927; 29180</t>
+          <t>17452; 30204</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18015; 31744</t>
+          <t>13579; 25229</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35002; 56371</t>
+          <t>33982; 51238</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>285</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>190614</t>
+          <t>218407</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>230710</t>
+          <t>191254</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>421324</t>
+          <t>409661</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>171505; 206428</t>
+          <t>196715; 239292</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>206255; 254849</t>
+          <t>173726; 207696</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>390425; 451243</t>
+          <t>379587; 437721</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>55033</t>
+          <t>56439</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60547</t>
+          <t>55540</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115580</t>
+          <t>111978</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45875; 63932</t>
+          <t>45865; 66925</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49677; 72384</t>
+          <t>46421; 65075</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100273; 131959</t>
+          <t>99306; 128390</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>400</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>266905</t>
+          <t>298448</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>315541</t>
+          <t>265810</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>582446</t>
+          <t>564258</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>245440; 286338</t>
+          <t>269880; 323279</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>290695; 342775</t>
+          <t>245778; 287328</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>546326; 619637</t>
+          <t>532683; 597201</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2906_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2906_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>43,94%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>43,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>32,49; 56,23</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30,15; 56,02</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>34,41; 51,89</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>45,88%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>42,45; 51,64</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>41,68; 49,83</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43,13; 49,73</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>34,36%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>38,69%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>36,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>27,92; 40,74</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>32,34; 45,33</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>32,26; 41,71</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>43,8%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43,85%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>39,61; 47,45</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>40,6; 47,46</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>41,4; 46,41</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4393948861363978</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4222658278866905</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4315831814973033</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>23602</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>19017</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42618</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.324895358402788</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.3015321295826574</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.344129174553968</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>17452; 30204</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13579; 25229</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>33982; 51238</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5622939454477649</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.5602189335565959</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.5188733648318812</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.471355687684978</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4588379490967879</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4654277473011866</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>218407</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>191254</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>409661</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4245404378430674</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4167873116887466</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4312599703080207</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>196715; 239292</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>173726; 207696</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>379587; 437721</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5164271511438623</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.4982858187072908</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.4973077339673674</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.3435824747882334</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3868708519000316</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3637708728620806</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>56439</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>55540</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>111978</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.2792094313207875</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3233543602771434</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3226041918719988</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>45865; 66925</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>46421; 65075</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>99306; 128390</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.4074198084228279</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4532934378735546</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.417084592676173</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4380309296072232</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4390521180875953</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4385113971153946</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>298448</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>265810</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>564258</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.3961016589335272</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4059638375767315</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4139731004138699</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>269880; 323279</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>245778; 287328</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>532683; 597201</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.4744745965083328</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4745945256971622</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.4641129160910339</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que recibieron lactancia mixta durante los primeros meses de vida (tasa de respuesta: 98,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>23602</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>19017</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>42618</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>17452</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>13579</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>33982</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>30204</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>25229</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>51238</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>297</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>285</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>218407</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>191254</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>409661</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>196715</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>173726</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>379587</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>239292</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>207696</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>437721</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>56439</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>55540</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>111978</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>45865</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>46421</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>99306</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>66925</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>65075</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>128390</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>413</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>298448</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>265810</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>564258</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>269880</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>245778</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>532683</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>323279</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>287328</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>597201</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>